--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/CONNECTICUT_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/CONNECTICUT_2016.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C128">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C365">
